--- a/data/trans_orig/P37C3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son efectivas en 2023</t>
+          <t>Población según la creencia de que las vacunas son efectivas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,74 +730,74 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10140</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2417</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,01%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2417</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39067</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27722</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61451</t>
+          <t>61188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114426</t>
+          <t>113358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154405</t>
+          <t>154195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111448</t>
+          <t>110090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140514</t>
+          <t>141597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>234663</t>
+          <t>233639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>284610</t>
+          <t>285997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441851</t>
+          <t>441923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484784</t>
+          <t>486186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502587</t>
+          <t>501145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534373</t>
+          <t>536326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>955687</t>
+          <t>953406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1013464</t>
+          <t>1011487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>15340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25125</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75128</t>
+          <t>73130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39534</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56807</t>
+          <t>55319</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106817</t>
+          <t>106299</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120181</t>
+          <t>119283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299448</t>
+          <t>293622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194056</t>
+          <t>191890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>235897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309842</t>
+          <t>293915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512608</t>
+          <t>512846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>800191</t>
+          <t>804206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1032493</t>
+          <t>1029032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>675818</t>
+          <t>676882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721686</t>
+          <t>725910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1505522</t>
+          <t>1502206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1755542</t>
+          <t>1769114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,76%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,82 +2109,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10379</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>14432</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2503</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9995</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5827</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>13685</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,47 +2257,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>9761</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4520</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>17282</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>9761</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>4930</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>17590</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>29647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63196</t>
+          <t>59046</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45237</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>43828</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95937</t>
+          <t>96028</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>181961</t>
+          <t>182028</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238468</t>
+          <t>238757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70510</t>
+          <t>80410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>202240</t>
+          <t>206007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>226100</t>
+          <t>231551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>426690</t>
+          <t>428607</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>410823</t>
+          <t>414271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>470852</t>
+          <t>472871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>682026</t>
+          <t>678522</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>835410</t>
+          <t>825594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1104953</t>
+          <t>1105807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1349647</t>
+          <t>1344449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31302</t>
+          <t>30048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69415</t>
+          <t>69755</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47128</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86661</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>91733</t>
+          <t>90385</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>142039</t>
+          <t>141151</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139268</t>
+          <t>140689</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>185925</t>
+          <t>191109</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153835</t>
+          <t>155177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218775</t>
+          <t>220026</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>309836</t>
+          <t>309696</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>390867</t>
+          <t>396253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>663981</t>
+          <t>660335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>717813</t>
+          <t>715071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>786548</t>
+          <t>784452</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>872923</t>
+          <t>870885</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1467187</t>
+          <t>1462377</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1568811</t>
+          <t>1566673</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32959</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70136</t>
+          <t>69553</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132818</t>
+          <t>132856</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>205386</t>
+          <t>207348</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109619</t>
+          <t>111912</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>168865</t>
+          <t>169206</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>265628</t>
+          <t>261405</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>358573</t>
+          <t>354722</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>557138</t>
+          <t>554366</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>807825</t>
+          <t>804524</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>559535</t>
+          <t>570025</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>752243</t>
+          <t>754026</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1232914</t>
+          <t>1207697</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1531337</t>
+          <t>1522007</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2396887</t>
+          <t>2399194</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2717496</t>
+          <t>2703046</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2701033</t>
+          <t>2701061</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2930938</t>
+          <t>2928813</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5135309</t>
+          <t>5141782</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5519165</t>
+          <t>5538950</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Habitat-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>22907</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39755</t>
+          <t>51735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35386</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61188</t>
+          <t>79785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>133167</t>
+          <t>147095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113358</t>
+          <t>126121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154195</t>
+          <t>169022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125290</t>
+          <t>135979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110090</t>
+          <t>119725</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141597</t>
+          <t>154913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>258457</t>
+          <t>283074</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233639</t>
+          <t>256382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285997</t>
+          <t>311156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>464161</t>
+          <t>493717</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441923</t>
+          <t>469035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486186</t>
+          <t>515768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>519209</t>
+          <t>561947</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501145</t>
+          <t>541033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536326</t>
+          <t>578824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>983368</t>
+          <t>1055664</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953406</t>
+          <t>1021333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1011487</t>
+          <t>1084050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>629045</t>
+          <t>683024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>629045</t>
+          <t>683024</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>629045</t>
+          <t>683024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>669857</t>
+          <t>726793</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>669857</t>
+          <t>726793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>669857</t>
+          <t>726793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1298901</t>
+          <t>1409817</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1298901</t>
+          <t>1409817</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1298901</t>
+          <t>1409817</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25995</t>
+          <t>26142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>60061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73130</t>
+          <t>79200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39230</t>
+          <t>44409</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>81851</t>
+          <t>94213</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55319</t>
+          <t>76813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106299</t>
+          <t>116358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>251611</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119283</t>
+          <t>221094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>293622</t>
+          <t>282429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>213937</t>
+          <t>235742</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191890</t>
+          <t>215355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>235897</t>
+          <t>261585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>440629</t>
+          <t>487354</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293915</t>
+          <t>450285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512846</t>
+          <t>531513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>891743</t>
+          <t>712268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>804206</t>
+          <t>678862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1029032</t>
+          <t>744421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>699819</t>
+          <t>785262</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>676882</t>
+          <t>758768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>725910</t>
+          <t>808225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1591562</t>
+          <t>1497530</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1502206</t>
+          <t>1455091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1769114</t>
+          <t>1538818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1183828</t>
+          <t>1037140</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1183828</t>
+          <t>1037140</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1183828</t>
+          <t>1037140</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>953790</t>
+          <t>1066205</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>953790</t>
+          <t>1066205</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>953790</t>
+          <t>1066205</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2137619</t>
+          <t>2103345</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2137619</t>
+          <t>2103345</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2137619</t>
+          <t>2103345</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>42195</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>37000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59046</t>
+          <t>70696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>81305</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>61875</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>96028</t>
+          <t>104616</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>207685</t>
+          <t>234157</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>182028</t>
+          <t>205305</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238757</t>
+          <t>263693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>150961</t>
+          <t>180572</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80410</t>
+          <t>160439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>206007</t>
+          <t>202340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>358646</t>
+          <t>414729</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>231551</t>
+          <t>380111</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>428607</t>
+          <t>458808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>443029</t>
+          <t>498371</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>414271</t>
+          <t>466380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>472871</t>
+          <t>529567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>744694</t>
+          <t>588448</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>678522</t>
+          <t>566365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>825594</t>
+          <t>612307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1187722</t>
+          <t>1086819</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1105807</t>
+          <t>1042060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1344449</t>
+          <t>1123178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>930191</t>
+          <t>808275</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>930191</t>
+          <t>808275</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>930191</t>
+          <t>808275</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1631834</t>
+          <t>1602736</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1631834</t>
+          <t>1602736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1631834</t>
+          <t>1602736</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,27 +2806,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51844</t>
+          <t>55587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38211</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69755</t>
+          <t>73096</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62185</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46022</t>
+          <t>50044</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85265</t>
+          <t>81838</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>114030</t>
+          <t>120452</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>90385</t>
+          <t>100689</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141151</t>
+          <t>143295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>161807</t>
+          <t>182067</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140689</t>
+          <t>156637</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191109</t>
+          <t>209273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>193752</t>
+          <t>214618</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155177</t>
+          <t>191139</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>220026</t>
+          <t>240459</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>355559</t>
+          <t>396685</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>309696</t>
+          <t>360526</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>396253</t>
+          <t>432453</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>690111</t>
+          <t>728072</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>660335</t>
+          <t>697878</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>715071</t>
+          <t>757166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>818730</t>
+          <t>822683</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>784452</t>
+          <t>794213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>870885</t>
+          <t>849860</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1508841</t>
+          <t>1550755</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1462377</t>
+          <t>1512978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1566673</t>
+          <t>1589518</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>919480</t>
+          <t>982968</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>919480</t>
+          <t>982968</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>919480</t>
+          <t>982968</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1084062</t>
+          <t>1111584</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1084062</t>
+          <t>1111584</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1084062</t>
+          <t>1111584</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2003542</t>
+          <t>2094553</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2003542</t>
+          <t>2094553</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2003542</t>
+          <t>2094553</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,102 +3453,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>12015</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>21796</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>13978</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>33947</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>11008</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>5785</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>21203</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>21410</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>12519</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>33850</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>51797</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,67 +3601,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>61582</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>48062</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>78088</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>54540</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>41756</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>69553</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>171711</t>
+          <t>201650</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132856</t>
+          <t>170487</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>207348</t>
+          <t>235387</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>139451</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>111912</t>
+          <t>130827</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>169206</t>
+          <t>177200</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>311163</t>
+          <t>354464</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>261405</t>
+          <t>320473</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>354722</t>
+          <t>396245</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>729351</t>
+          <t>814931</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>554366</t>
+          <t>758800</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>804524</t>
+          <t>873374</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>683939</t>
+          <t>766911</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>570025</t>
+          <t>726535</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>754026</t>
+          <t>812008</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1413290</t>
+          <t>1581842</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1207697</t>
+          <t>1511301</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1522007</t>
+          <t>1650635</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2489042</t>
+          <t>2432427</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2399194</t>
+          <t>2372909</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2703046</t>
+          <t>2494912</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2782451</t>
+          <t>2758340</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2701061</t>
+          <t>2711924</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2928813</t>
+          <t>2804954</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5271493</t>
+          <t>5190767</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5141782</t>
+          <t>5114348</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5538950</t>
+          <t>5263986</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
